--- a/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1_mtd_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_16S_filt_Dataset_1_mtd_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">MS_004</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_006</t>
+    <t xml:space="preserve">MS_008</t>
   </si>
   <si>
     <t xml:space="preserve">Fruits_0days</t>
@@ -125,6 +125,69 @@
     <t xml:space="preserve">Fruit</t>
   </si>
   <si>
+    <t xml:space="preserve">CH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN_CH_CDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOM_CH_CDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IST_ST_CIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIL_ST_MDB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G0_Adults_Fruits_2days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mother</t>
+  </si>
+  <si>
     <t xml:space="preserve">BL</t>
   </si>
   <si>
@@ -137,72 +200,6 @@
     <t xml:space="preserve">VAR_BL_LOC</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIN_CH_CDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOM_CH_CDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IST_ST_CIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIL_ST_MDB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS_023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G0_Adults_Fruits_2days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mother</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_024</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
     <t xml:space="preserve">MS_026</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_027</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_028</t>
   </si>
   <si>
@@ -272,6 +272,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -293,18 +299,21 @@
     <t xml:space="preserve">MS_072</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1_Larvae_Fruits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DaughterLarva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larva</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_086</t>
   </si>
   <si>
-    <t xml:space="preserve">G1_Larvae_Fruits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DaughterLarva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larva</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_087</t>
   </si>
   <si>
@@ -518,9 +527,6 @@
     <t xml:space="preserve">MS_188</t>
   </si>
   <si>
-    <t xml:space="preserve">MS_190</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_231</t>
   </si>
   <si>
@@ -642,6 +648,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS_269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_270</t>
   </si>
   <si>
     <t xml:space="preserve">MS_271</t>
@@ -1303,16 +1312,16 @@
         <v>36</v>
       </c>
       <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" t="s">
         <v>42</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>43</v>
-      </c>
-      <c r="L6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" t="s">
-        <v>45</v>
       </c>
       <c r="N6" t="s">
         <v>27</v>
@@ -1335,10 +1344,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -1362,10 +1371,10 @@
         <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L7" t="s">
         <v>47</v>
@@ -1389,7 +1398,7 @@
         <v>33</v>
       </c>
       <c r="S7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -1397,7 +1406,7 @@
         <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
@@ -1421,16 +1430,16 @@
         <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N8" t="s">
         <v>27</v>
@@ -1453,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -1465,7 +1474,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -1480,16 +1489,16 @@
         <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
         <v>27</v>
@@ -1507,7 +1516,7 @@
         <v>33</v>
       </c>
       <c r="S9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1521,49 +1530,49 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="s">
         <v>57</v>
       </c>
-      <c r="L10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>27</v>
-      </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="S10" t="s">
         <v>55</v>
@@ -1571,22 +1580,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -1598,16 +1607,16 @@
         <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="N11" t="s">
         <v>27</v>
@@ -1619,13 +1628,13 @@
         <v>28</v>
       </c>
       <c r="Q11" t="s">
+        <v>57</v>
+      </c>
+      <c r="R11" t="s">
+        <v>57</v>
+      </c>
+      <c r="S11" t="s">
         <v>62</v>
-      </c>
-      <c r="R11" t="s">
-        <v>62</v>
-      </c>
-      <c r="S11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -1633,19 +1642,19 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -1663,10 +1672,10 @@
         <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N12" t="s">
         <v>27</v>
@@ -1678,10 +1687,10 @@
         <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S12" t="s">
         <v>63</v>
@@ -1692,19 +1701,19 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -1716,17 +1725,17 @@
         <v>36</v>
       </c>
       <c r="J13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" t="s">
         <v>42</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>43</v>
       </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
       <c r="N13" t="s">
         <v>27</v>
       </c>
@@ -1737,10 +1746,10 @@
         <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S13" t="s">
         <v>64</v>
@@ -1751,19 +1760,19 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -1775,16 +1784,16 @@
         <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N14" t="s">
         <v>27</v>
@@ -1796,10 +1805,10 @@
         <v>28</v>
       </c>
       <c r="Q14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S14" t="s">
         <v>65</v>
@@ -1816,13 +1825,13 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
@@ -1834,16 +1843,16 @@
         <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L15" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N15" t="s">
         <v>27</v>
@@ -1855,10 +1864,10 @@
         <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S15" t="s">
         <v>66</v>
@@ -1875,13 +1884,13 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
@@ -1893,16 +1902,16 @@
         <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N16" t="s">
         <v>27</v>
@@ -1914,10 +1923,10 @@
         <v>28</v>
       </c>
       <c r="Q16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S16" t="s">
         <v>67</v>
@@ -1934,13 +1943,13 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -1952,31 +1961,31 @@
         <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" t="s">
         <v>57</v>
       </c>
-      <c r="L17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M17" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>62</v>
-      </c>
       <c r="R17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S17" t="s">
         <v>68</v>
@@ -1993,13 +2002,13 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
@@ -2011,16 +2020,16 @@
         <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K18" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="N18" t="s">
         <v>27</v>
@@ -2032,10 +2041,10 @@
         <v>28</v>
       </c>
       <c r="Q18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S18" t="s">
         <v>70</v>
@@ -2052,13 +2061,13 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
         <v>25</v>
@@ -2070,16 +2079,16 @@
         <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K19" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M19" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N19" t="s">
         <v>27</v>
@@ -2091,10 +2100,10 @@
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S19" t="s">
         <v>71</v>
@@ -2111,13 +2120,13 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
@@ -2129,16 +2138,16 @@
         <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N20" t="s">
         <v>27</v>
@@ -2150,10 +2159,10 @@
         <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S20" t="s">
         <v>72</v>
@@ -2170,13 +2179,13 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
@@ -2188,16 +2197,16 @@
         <v>36</v>
       </c>
       <c r="J21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N21" t="s">
         <v>27</v>
@@ -2209,10 +2218,10 @@
         <v>28</v>
       </c>
       <c r="Q21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S21" t="s">
         <v>73</v>
@@ -2229,13 +2238,13 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -2247,16 +2256,16 @@
         <v>36</v>
       </c>
       <c r="J22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M22" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N22" t="s">
         <v>27</v>
@@ -2268,10 +2277,10 @@
         <v>28</v>
       </c>
       <c r="Q22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S22" t="s">
         <v>74</v>
@@ -2288,13 +2297,13 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
@@ -2306,31 +2315,31 @@
         <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K23" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23" t="s">
         <v>57</v>
       </c>
-      <c r="L23" t="s">
-        <v>58</v>
-      </c>
-      <c r="M23" t="s">
-        <v>59</v>
-      </c>
-      <c r="N23" t="s">
-        <v>27</v>
-      </c>
-      <c r="O23" t="s">
-        <v>27</v>
-      </c>
-      <c r="P23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>62</v>
-      </c>
       <c r="R23" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S23" t="s">
         <v>75</v>
@@ -2347,13 +2356,13 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
@@ -2365,31 +2374,31 @@
         <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L24" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24" t="s">
         <v>57</v>
       </c>
-      <c r="L24" t="s">
-        <v>58</v>
-      </c>
-      <c r="M24" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>62</v>
-      </c>
       <c r="R24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S24" t="s">
         <v>76</v>
@@ -2424,16 +2433,16 @@
         <v>36</v>
       </c>
       <c r="J25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" t="s">
         <v>42</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>43</v>
-      </c>
-      <c r="L25" t="s">
-        <v>47</v>
-      </c>
-      <c r="M25" t="s">
-        <v>48</v>
       </c>
       <c r="N25" t="s">
         <v>27</v>
@@ -2483,16 +2492,16 @@
         <v>36</v>
       </c>
       <c r="J26" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" t="s">
         <v>42</v>
       </c>
-      <c r="K26" t="s">
+      <c r="M26" t="s">
         <v>43</v>
-      </c>
-      <c r="L26" t="s">
-        <v>47</v>
-      </c>
-      <c r="M26" t="s">
-        <v>48</v>
       </c>
       <c r="N26" t="s">
         <v>27</v>
@@ -2542,16 +2551,16 @@
         <v>36</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N27" t="s">
         <v>27</v>
@@ -2601,16 +2610,16 @@
         <v>36</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L28" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N28" t="s">
         <v>27</v>
@@ -2660,16 +2669,16 @@
         <v>36</v>
       </c>
       <c r="J29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L29" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M29" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N29" t="s">
         <v>27</v>
@@ -2719,16 +2728,16 @@
         <v>36</v>
       </c>
       <c r="J30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K30" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L30" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N30" t="s">
         <v>27</v>
@@ -2778,16 +2787,16 @@
         <v>36</v>
       </c>
       <c r="J31" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M31" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N31" t="s">
         <v>27</v>
@@ -2837,16 +2846,16 @@
         <v>36</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L32" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M32" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N32" t="s">
         <v>27</v>
@@ -2881,7 +2890,7 @@
         <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>79</v>
@@ -2896,16 +2905,16 @@
         <v>36</v>
       </c>
       <c r="J33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L33" t="s">
         <v>42</v>
       </c>
-      <c r="K33" t="s">
+      <c r="M33" t="s">
         <v>43</v>
-      </c>
-      <c r="L33" t="s">
-        <v>44</v>
-      </c>
-      <c r="M33" t="s">
-        <v>45</v>
       </c>
       <c r="N33" t="s">
         <v>27</v>
@@ -2940,7 +2949,7 @@
         <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
         <v>79</v>
@@ -2955,16 +2964,16 @@
         <v>36</v>
       </c>
       <c r="J34" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" t="s">
         <v>42</v>
       </c>
-      <c r="K34" t="s">
+      <c r="M34" t="s">
         <v>43</v>
-      </c>
-      <c r="L34" t="s">
-        <v>44</v>
-      </c>
-      <c r="M34" t="s">
-        <v>45</v>
       </c>
       <c r="N34" t="s">
         <v>27</v>
@@ -2999,7 +3008,7 @@
         <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
         <v>79</v>
@@ -3014,16 +3023,16 @@
         <v>36</v>
       </c>
       <c r="J35" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K35" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L35" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M35" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N35" t="s">
         <v>27</v>
@@ -3058,7 +3067,7 @@
         <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
         <v>79</v>
@@ -3073,16 +3082,16 @@
         <v>36</v>
       </c>
       <c r="J36" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K36" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L36" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M36" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N36" t="s">
         <v>27</v>
@@ -3108,7 +3117,7 @@
         <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
         <v>21</v>
@@ -3132,16 +3141,16 @@
         <v>36</v>
       </c>
       <c r="J37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K37" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L37" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M37" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N37" t="s">
         <v>27</v>
@@ -3173,34 +3182,34 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
         <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I38" t="s">
         <v>36</v>
       </c>
       <c r="J38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K38" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M38" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N38" t="s">
         <v>27</v>
@@ -3212,10 +3221,10 @@
         <v>28</v>
       </c>
       <c r="Q38" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="R38" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="S38" t="s">
         <v>93</v>
@@ -3223,43 +3232,43 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
         <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
         <v>36</v>
       </c>
       <c r="J39" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K39" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M39" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N39" t="s">
         <v>27</v>
@@ -3271,18 +3280,18 @@
         <v>28</v>
       </c>
       <c r="Q39" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="R39" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="S39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
@@ -3291,13 +3300,13 @@
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
         <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
@@ -3309,16 +3318,16 @@
         <v>36</v>
       </c>
       <c r="J40" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K40" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L40" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M40" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N40" t="s">
         <v>27</v>
@@ -3330,13 +3339,13 @@
         <v>28</v>
       </c>
       <c r="Q40" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R40" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
@@ -3350,13 +3359,13 @@
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -3368,16 +3377,16 @@
         <v>36</v>
       </c>
       <c r="J41" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K41" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L41" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M41" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N41" t="s">
         <v>27</v>
@@ -3389,10 +3398,10 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S41" t="s">
         <v>99</v>
@@ -3409,13 +3418,13 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -3427,16 +3436,16 @@
         <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K42" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L42" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M42" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N42" t="s">
         <v>27</v>
@@ -3448,10 +3457,10 @@
         <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R42" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S42" t="s">
         <v>100</v>
@@ -3462,19 +3471,19 @@
         <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43" t="s">
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -3486,16 +3495,16 @@
         <v>36</v>
       </c>
       <c r="J43" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K43" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L43" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M43" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N43" t="s">
         <v>27</v>
@@ -3507,10 +3516,10 @@
         <v>28</v>
       </c>
       <c r="Q43" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R43" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S43" t="s">
         <v>101</v>
@@ -3521,19 +3530,19 @@
         <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -3545,16 +3554,16 @@
         <v>36</v>
       </c>
       <c r="J44" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K44" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L44" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="M44" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="N44" t="s">
         <v>27</v>
@@ -3566,10 +3575,10 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R44" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S44" t="s">
         <v>102</v>
@@ -3586,34 +3595,34 @@
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I45" t="s">
         <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L45" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M45" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N45" t="s">
         <v>27</v>
@@ -3625,10 +3634,10 @@
         <v>28</v>
       </c>
       <c r="Q45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S45" t="s">
         <v>103</v>
@@ -3645,34 +3654,34 @@
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I46" t="s">
         <v>36</v>
       </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L46" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M46" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N46" t="s">
         <v>27</v>
@@ -3684,10 +3693,10 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S46" t="s">
         <v>104</v>
@@ -3704,34 +3713,34 @@
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
       </c>
       <c r="H47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I47" t="s">
         <v>36</v>
       </c>
       <c r="J47" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L47" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M47" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N47" t="s">
         <v>27</v>
@@ -3743,10 +3752,10 @@
         <v>28</v>
       </c>
       <c r="Q47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S47" t="s">
         <v>105</v>
@@ -3763,13 +3772,13 @@
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
@@ -3781,16 +3790,16 @@
         <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L48" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M48" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N48" t="s">
         <v>27</v>
@@ -3802,10 +3811,10 @@
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S48" t="s">
         <v>106</v>
@@ -3822,13 +3831,13 @@
         <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
         <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
@@ -3840,16 +3849,16 @@
         <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K49" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L49" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M49" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N49" t="s">
         <v>27</v>
@@ -3861,10 +3870,10 @@
         <v>28</v>
       </c>
       <c r="Q49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S49" t="s">
         <v>107</v>
@@ -3881,13 +3890,13 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
@@ -3899,16 +3908,16 @@
         <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K50" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L50" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M50" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N50" t="s">
         <v>27</v>
@@ -3920,10 +3929,10 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S50" t="s">
         <v>108</v>
@@ -3934,19 +3943,19 @@
         <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E51" t="s">
         <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
@@ -3958,16 +3967,16 @@
         <v>36</v>
       </c>
       <c r="J51" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K51" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L51" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M51" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N51" t="s">
         <v>27</v>
@@ -3979,10 +3988,10 @@
         <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S51" t="s">
         <v>109</v>
@@ -3993,19 +4002,19 @@
         <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C52" t="s">
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E52" t="s">
         <v>23</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -4017,16 +4026,16 @@
         <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K52" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L52" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="M52" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="N52" t="s">
         <v>27</v>
@@ -4038,10 +4047,10 @@
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R52" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S52" t="s">
         <v>110</v>
@@ -4052,19 +4061,19 @@
         <v>111</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
         <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E53" t="s">
         <v>23</v>
       </c>
       <c r="F53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -4076,16 +4085,16 @@
         <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K53" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L53" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M53" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N53" t="s">
         <v>27</v>
@@ -4097,10 +4106,10 @@
         <v>28</v>
       </c>
       <c r="Q53" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R53" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S53" t="s">
         <v>111</v>
@@ -4111,55 +4120,55 @@
         <v>112</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E54" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F54" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
       </c>
       <c r="H54" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I54" t="s">
         <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L54" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M54" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N54" t="s">
         <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P54" t="s">
         <v>28</v>
       </c>
       <c r="Q54" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="R54" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="S54" t="s">
         <v>112</v>
@@ -4167,125 +4176,125 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
         <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E55" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I55" t="s">
         <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K55" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L55" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M55" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N55" t="s">
         <v>27</v>
       </c>
       <c r="O55" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P55" t="s">
         <v>28</v>
       </c>
       <c r="Q55" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="R55" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="S55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E56" t="s">
         <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I56" t="s">
         <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K56" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L56" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M56" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N56" t="s">
         <v>27</v>
       </c>
       <c r="O56" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P56" t="s">
         <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="R56" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="S56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
         <v>21</v>
@@ -4294,13 +4303,13 @@
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -4312,34 +4321,34 @@
         <v>36</v>
       </c>
       <c r="J57" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L57" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M57" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N57" t="s">
         <v>27</v>
       </c>
       <c r="O57" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="P57" t="s">
         <v>28</v>
       </c>
       <c r="Q57" t="s">
+        <v>118</v>
+      </c>
+      <c r="R57" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" t="s">
         <v>115</v>
-      </c>
-      <c r="R57" t="s">
-        <v>27</v>
-      </c>
-      <c r="S57" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="58">
@@ -4353,13 +4362,13 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -4371,28 +4380,28 @@
         <v>36</v>
       </c>
       <c r="J58" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K58" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L58" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M58" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N58" t="s">
         <v>27</v>
       </c>
       <c r="O58" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P58" t="s">
         <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R58" t="s">
         <v>27</v>
@@ -4412,13 +4421,13 @@
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E59" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
@@ -4430,28 +4439,28 @@
         <v>36</v>
       </c>
       <c r="J59" t="s">
+        <v>37</v>
+      </c>
+      <c r="K59" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" t="s">
         <v>42</v>
       </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>43</v>
       </c>
-      <c r="L59" t="s">
-        <v>44</v>
-      </c>
-      <c r="M59" t="s">
-        <v>45</v>
-      </c>
       <c r="N59" t="s">
         <v>27</v>
       </c>
       <c r="O59" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P59" t="s">
         <v>28</v>
       </c>
       <c r="Q59" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R59" t="s">
         <v>27</v>
@@ -4471,13 +4480,13 @@
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
@@ -4489,28 +4498,28 @@
         <v>36</v>
       </c>
       <c r="J60" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K60" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L60" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M60" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N60" t="s">
         <v>27</v>
       </c>
       <c r="O60" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P60" t="s">
         <v>28</v>
       </c>
       <c r="Q60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R60" t="s">
         <v>27</v>
@@ -4530,13 +4539,13 @@
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
@@ -4548,28 +4557,28 @@
         <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K61" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L61" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M61" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="N61" t="s">
         <v>27</v>
       </c>
       <c r="O61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P61" t="s">
         <v>28</v>
       </c>
       <c r="Q61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R61" t="s">
         <v>27</v>
@@ -4589,13 +4598,13 @@
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E62" t="s">
         <v>69</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
@@ -4607,28 +4616,28 @@
         <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K62" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L62" t="s">
+        <v>39</v>
+      </c>
+      <c r="M62" t="s">
+        <v>40</v>
+      </c>
+      <c r="N62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" t="s">
         <v>58</v>
       </c>
-      <c r="M62" t="s">
-        <v>59</v>
-      </c>
-      <c r="N62" t="s">
-        <v>27</v>
-      </c>
-      <c r="O62" t="s">
-        <v>42</v>
-      </c>
       <c r="P62" t="s">
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R62" t="s">
         <v>27</v>
@@ -4648,13 +4657,13 @@
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E63" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -4666,28 +4675,28 @@
         <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K63" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L63" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M63" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N63" t="s">
         <v>27</v>
       </c>
       <c r="O63" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P63" t="s">
         <v>28</v>
       </c>
       <c r="Q63" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R63" t="s">
         <v>27</v>
@@ -4707,46 +4716,46 @@
         <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
       </c>
       <c r="H64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I64" t="s">
         <v>36</v>
       </c>
       <c r="J64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L64" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M64" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N64" t="s">
         <v>27</v>
       </c>
       <c r="O64" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P64" t="s">
         <v>28</v>
       </c>
       <c r="Q64" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R64" t="s">
         <v>27</v>
@@ -4766,46 +4775,46 @@
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E65" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F65" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
       </c>
       <c r="H65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I65" t="s">
         <v>36</v>
       </c>
       <c r="J65" t="s">
+        <v>45</v>
+      </c>
+      <c r="K65" t="s">
+        <v>52</v>
+      </c>
+      <c r="L65" t="s">
+        <v>53</v>
+      </c>
+      <c r="M65" t="s">
+        <v>54</v>
+      </c>
+      <c r="N65" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" t="s">
         <v>37</v>
       </c>
-      <c r="K65" t="s">
-        <v>38</v>
-      </c>
-      <c r="L65" t="s">
-        <v>39</v>
-      </c>
-      <c r="M65" t="s">
-        <v>40</v>
-      </c>
-      <c r="N65" t="s">
-        <v>27</v>
-      </c>
-      <c r="O65" t="s">
-        <v>50</v>
-      </c>
       <c r="P65" t="s">
         <v>28</v>
       </c>
       <c r="Q65" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R65" t="s">
         <v>27</v>
@@ -4825,46 +4834,46 @@
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E66" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F66" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I66" t="s">
         <v>36</v>
       </c>
       <c r="J66" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L66" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M66" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N66" t="s">
         <v>27</v>
       </c>
       <c r="O66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P66" t="s">
         <v>28</v>
       </c>
       <c r="Q66" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R66" t="s">
         <v>27</v>
@@ -4884,13 +4893,13 @@
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -4902,28 +4911,28 @@
         <v>36</v>
       </c>
       <c r="J67" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L67" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M67" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N67" t="s">
         <v>27</v>
       </c>
       <c r="O67" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="P67" t="s">
         <v>28</v>
       </c>
       <c r="Q67" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R67" t="s">
         <v>27</v>
@@ -4943,13 +4952,13 @@
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E68" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F68" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -4961,28 +4970,28 @@
         <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K68" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L68" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M68" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N68" t="s">
         <v>27</v>
       </c>
       <c r="O68" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P68" t="s">
         <v>28</v>
       </c>
       <c r="Q68" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R68" t="s">
         <v>27</v>
@@ -5002,13 +5011,13 @@
         <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E69" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -5020,28 +5029,28 @@
         <v>36</v>
       </c>
       <c r="J69" t="s">
+        <v>37</v>
+      </c>
+      <c r="K69" t="s">
+        <v>38</v>
+      </c>
+      <c r="L69" t="s">
         <v>42</v>
       </c>
-      <c r="K69" t="s">
+      <c r="M69" t="s">
         <v>43</v>
       </c>
-      <c r="L69" t="s">
-        <v>44</v>
-      </c>
-      <c r="M69" t="s">
-        <v>45</v>
-      </c>
       <c r="N69" t="s">
         <v>27</v>
       </c>
       <c r="O69" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P69" t="s">
         <v>28</v>
       </c>
       <c r="Q69" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R69" t="s">
         <v>27</v>
@@ -5061,13 +5070,13 @@
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E70" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F70" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -5079,28 +5088,28 @@
         <v>36</v>
       </c>
       <c r="J70" t="s">
+        <v>37</v>
+      </c>
+      <c r="K70" t="s">
+        <v>38</v>
+      </c>
+      <c r="L70" t="s">
         <v>42</v>
       </c>
-      <c r="K70" t="s">
+      <c r="M70" t="s">
         <v>43</v>
       </c>
-      <c r="L70" t="s">
-        <v>44</v>
-      </c>
-      <c r="M70" t="s">
-        <v>45</v>
-      </c>
       <c r="N70" t="s">
         <v>27</v>
       </c>
       <c r="O70" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P70" t="s">
         <v>28</v>
       </c>
       <c r="Q70" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R70" t="s">
         <v>27</v>
@@ -5120,13 +5129,13 @@
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E71" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -5138,28 +5147,28 @@
         <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K71" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L71" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M71" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N71" t="s">
         <v>27</v>
       </c>
       <c r="O71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P71" t="s">
         <v>28</v>
       </c>
       <c r="Q71" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R71" t="s">
         <v>27</v>
@@ -5179,13 +5188,13 @@
         <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F72" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -5197,28 +5206,28 @@
         <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K72" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L72" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M72" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N72" t="s">
         <v>27</v>
       </c>
       <c r="O72" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="P72" t="s">
         <v>28</v>
       </c>
       <c r="Q72" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R72" t="s">
         <v>27</v>
@@ -5238,13 +5247,13 @@
         <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E73" t="s">
         <v>69</v>
       </c>
       <c r="F73" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -5256,28 +5265,28 @@
         <v>36</v>
       </c>
       <c r="J73" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K73" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L73" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M73" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N73" t="s">
         <v>27</v>
       </c>
       <c r="O73" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P73" t="s">
         <v>28</v>
       </c>
       <c r="Q73" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R73" t="s">
         <v>27</v>
@@ -5297,13 +5306,13 @@
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E74" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F74" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -5315,28 +5324,28 @@
         <v>36</v>
       </c>
       <c r="J74" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K74" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L74" t="s">
+        <v>47</v>
+      </c>
+      <c r="M74" t="s">
+        <v>48</v>
+      </c>
+      <c r="N74" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74" t="s">
         <v>58</v>
       </c>
-      <c r="M74" t="s">
-        <v>59</v>
-      </c>
-      <c r="N74" t="s">
-        <v>27</v>
-      </c>
-      <c r="O74" t="s">
-        <v>50</v>
-      </c>
       <c r="P74" t="s">
         <v>28</v>
       </c>
       <c r="Q74" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R74" t="s">
         <v>27</v>
@@ -5356,34 +5365,34 @@
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E75" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F75" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I75" t="s">
         <v>36</v>
       </c>
       <c r="J75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K75" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L75" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M75" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N75" t="s">
         <v>27</v>
@@ -5395,7 +5404,7 @@
         <v>28</v>
       </c>
       <c r="Q75" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="R75" t="s">
         <v>27</v>
@@ -5406,7 +5415,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
         <v>21</v>
@@ -5415,57 +5424,57 @@
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E76" t="s">
         <v>69</v>
       </c>
       <c r="F76" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="G76" t="s">
         <v>25</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I76" t="s">
         <v>36</v>
       </c>
       <c r="J76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K76" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M76" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N76" t="s">
         <v>27</v>
       </c>
       <c r="O76" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P76" t="s">
         <v>28</v>
       </c>
       <c r="Q76" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="R76" t="s">
         <v>27</v>
       </c>
       <c r="S76" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B77" t="s">
         <v>21</v>
@@ -5474,57 +5483,57 @@
         <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E77" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F77" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="G77" t="s">
         <v>25</v>
       </c>
       <c r="H77" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I77" t="s">
         <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K77" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L77" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="M77" t="s">
+        <v>54</v>
+      </c>
+      <c r="N77" t="s">
+        <v>27</v>
+      </c>
+      <c r="O77" t="s">
         <v>45</v>
       </c>
-      <c r="N77" t="s">
-        <v>27</v>
-      </c>
-      <c r="O77" t="s">
-        <v>42</v>
-      </c>
       <c r="P77" t="s">
         <v>28</v>
       </c>
       <c r="Q77" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="R77" t="s">
         <v>27</v>
       </c>
       <c r="S77" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B78" t="s">
         <v>21</v>
@@ -5533,13 +5542,13 @@
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="F78" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G78" t="s">
         <v>25</v>
@@ -5551,34 +5560,34 @@
         <v>36</v>
       </c>
       <c r="J78" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L78" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M78" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N78" t="s">
         <v>27</v>
       </c>
       <c r="O78" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P78" t="s">
         <v>28</v>
       </c>
       <c r="Q78" t="s">
+        <v>142</v>
+      </c>
+      <c r="R78" t="s">
+        <v>27</v>
+      </c>
+      <c r="S78" t="s">
         <v>139</v>
-      </c>
-      <c r="R78" t="s">
-        <v>27</v>
-      </c>
-      <c r="S78" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="79">
@@ -5592,13 +5601,13 @@
         <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F79" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G79" t="s">
         <v>25</v>
@@ -5610,28 +5619,28 @@
         <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K79" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L79" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M79" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N79" t="s">
         <v>27</v>
       </c>
       <c r="O79" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P79" t="s">
         <v>28</v>
       </c>
       <c r="Q79" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R79" t="s">
         <v>27</v>
@@ -5651,13 +5660,13 @@
         <v>20</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F80" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G80" t="s">
         <v>25</v>
@@ -5669,28 +5678,28 @@
         <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K80" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L80" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M80" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N80" t="s">
         <v>27</v>
       </c>
       <c r="O80" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P80" t="s">
         <v>28</v>
       </c>
       <c r="Q80" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R80" t="s">
         <v>27</v>
@@ -5710,13 +5719,13 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F81" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G81" t="s">
         <v>25</v>
@@ -5728,28 +5737,28 @@
         <v>36</v>
       </c>
       <c r="J81" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K81" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L81" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="M81" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="N81" t="s">
         <v>27</v>
       </c>
       <c r="O81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P81" t="s">
         <v>28</v>
       </c>
       <c r="Q81" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R81" t="s">
         <v>27</v>
@@ -5769,13 +5778,13 @@
         <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G82" t="s">
         <v>25</v>
@@ -5787,28 +5796,28 @@
         <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K82" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L82" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M82" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N82" t="s">
         <v>27</v>
       </c>
       <c r="O82" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P82" t="s">
         <v>28</v>
       </c>
       <c r="Q82" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R82" t="s">
         <v>27</v>
@@ -5828,13 +5837,13 @@
         <v>20</v>
       </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F83" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G83" t="s">
         <v>25</v>
@@ -5846,28 +5855,28 @@
         <v>36</v>
       </c>
       <c r="J83" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K83" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L83" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M83" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N83" t="s">
         <v>27</v>
       </c>
       <c r="O83" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P83" t="s">
         <v>28</v>
       </c>
       <c r="Q83" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R83" t="s">
         <v>27</v>
@@ -5887,46 +5896,46 @@
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E84" t="s">
         <v>23</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G84" t="s">
         <v>25</v>
       </c>
       <c r="H84" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I84" t="s">
         <v>36</v>
       </c>
       <c r="J84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K84" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L84" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M84" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N84" t="s">
         <v>27</v>
       </c>
       <c r="O84" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P84" t="s">
         <v>28</v>
       </c>
       <c r="Q84" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R84" t="s">
         <v>27</v>
@@ -5946,34 +5955,34 @@
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E85" t="s">
         <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G85" t="s">
         <v>25</v>
       </c>
       <c r="H85" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I85" t="s">
         <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K85" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L85" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M85" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N85" t="s">
         <v>27</v>
@@ -5985,7 +5994,7 @@
         <v>28</v>
       </c>
       <c r="Q85" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R85" t="s">
         <v>27</v>
@@ -6005,46 +6014,46 @@
         <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E86" t="s">
         <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G86" t="s">
         <v>25</v>
       </c>
       <c r="H86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I86" t="s">
         <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K86" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L86" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M86" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N86" t="s">
         <v>27</v>
       </c>
       <c r="O86" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P86" t="s">
         <v>28</v>
       </c>
       <c r="Q86" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R86" t="s">
         <v>27</v>
@@ -6064,13 +6073,13 @@
         <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G87" t="s">
         <v>25</v>
@@ -6082,28 +6091,28 @@
         <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K87" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L87" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M87" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N87" t="s">
         <v>27</v>
       </c>
       <c r="O87" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P87" t="s">
         <v>28</v>
       </c>
       <c r="Q87" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R87" t="s">
         <v>27</v>
@@ -6123,13 +6132,13 @@
         <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E88" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G88" t="s">
         <v>25</v>
@@ -6141,28 +6150,28 @@
         <v>36</v>
       </c>
       <c r="J88" t="s">
+        <v>37</v>
+      </c>
+      <c r="K88" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" t="s">
         <v>42</v>
       </c>
-      <c r="K88" t="s">
+      <c r="M88" t="s">
         <v>43</v>
       </c>
-      <c r="L88" t="s">
-        <v>44</v>
-      </c>
-      <c r="M88" t="s">
-        <v>45</v>
-      </c>
       <c r="N88" t="s">
         <v>27</v>
       </c>
       <c r="O88" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P88" t="s">
         <v>28</v>
       </c>
       <c r="Q88" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R88" t="s">
         <v>27</v>
@@ -6182,13 +6191,13 @@
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
@@ -6200,28 +6209,28 @@
         <v>36</v>
       </c>
       <c r="J89" t="s">
+        <v>37</v>
+      </c>
+      <c r="K89" t="s">
+        <v>38</v>
+      </c>
+      <c r="L89" t="s">
         <v>42</v>
       </c>
-      <c r="K89" t="s">
+      <c r="M89" t="s">
         <v>43</v>
       </c>
-      <c r="L89" t="s">
-        <v>44</v>
-      </c>
-      <c r="M89" t="s">
-        <v>45</v>
-      </c>
       <c r="N89" t="s">
         <v>27</v>
       </c>
       <c r="O89" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P89" t="s">
         <v>28</v>
       </c>
       <c r="Q89" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R89" t="s">
         <v>27</v>
@@ -6241,13 +6250,13 @@
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E90" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F90" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G90" t="s">
         <v>25</v>
@@ -6259,28 +6268,28 @@
         <v>36</v>
       </c>
       <c r="J90" t="s">
+        <v>37</v>
+      </c>
+      <c r="K90" t="s">
+        <v>38</v>
+      </c>
+      <c r="L90" t="s">
         <v>42</v>
       </c>
-      <c r="K90" t="s">
+      <c r="M90" t="s">
         <v>43</v>
       </c>
-      <c r="L90" t="s">
-        <v>44</v>
-      </c>
-      <c r="M90" t="s">
+      <c r="N90" t="s">
+        <v>27</v>
+      </c>
+      <c r="O90" t="s">
         <v>45</v>
       </c>
-      <c r="N90" t="s">
-        <v>27</v>
-      </c>
-      <c r="O90" t="s">
-        <v>50</v>
-      </c>
       <c r="P90" t="s">
         <v>28</v>
       </c>
       <c r="Q90" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R90" t="s">
         <v>27</v>
@@ -6300,13 +6309,13 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E91" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F91" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G91" t="s">
         <v>25</v>
@@ -6318,28 +6327,28 @@
         <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K91" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L91" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M91" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N91" t="s">
         <v>27</v>
       </c>
       <c r="O91" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="P91" t="s">
         <v>28</v>
       </c>
       <c r="Q91" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R91" t="s">
         <v>27</v>
@@ -6359,13 +6368,13 @@
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E92" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F92" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G92" t="s">
         <v>25</v>
@@ -6377,28 +6386,28 @@
         <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K92" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L92" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M92" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N92" t="s">
         <v>27</v>
       </c>
       <c r="O92" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
       </c>
       <c r="Q92" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R92" t="s">
         <v>27</v>
@@ -6418,13 +6427,13 @@
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F93" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G93" t="s">
         <v>25</v>
@@ -6436,28 +6445,28 @@
         <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K93" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L93" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M93" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N93" t="s">
         <v>27</v>
       </c>
       <c r="O93" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P93" t="s">
         <v>28</v>
       </c>
       <c r="Q93" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R93" t="s">
         <v>27</v>
@@ -6477,13 +6486,13 @@
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E94" t="s">
         <v>23</v>
       </c>
       <c r="F94" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G94" t="s">
         <v>25</v>
@@ -6495,28 +6504,28 @@
         <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K94" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L94" t="s">
+        <v>47</v>
+      </c>
+      <c r="M94" t="s">
+        <v>48</v>
+      </c>
+      <c r="N94" t="s">
+        <v>27</v>
+      </c>
+      <c r="O94" t="s">
         <v>58</v>
       </c>
-      <c r="M94" t="s">
-        <v>59</v>
-      </c>
-      <c r="N94" t="s">
-        <v>27</v>
-      </c>
-      <c r="O94" t="s">
-        <v>42</v>
-      </c>
       <c r="P94" t="s">
         <v>28</v>
       </c>
       <c r="Q94" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R94" t="s">
         <v>27</v>
@@ -6533,31 +6542,31 @@
         <v>21</v>
       </c>
       <c r="C95" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E95" t="s">
         <v>23</v>
       </c>
       <c r="F95" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="G95" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I95" t="s">
         <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K95" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L95" t="s">
         <v>47</v>
@@ -6566,19 +6575,19 @@
         <v>48</v>
       </c>
       <c r="N95" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
       <c r="O95" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P95" t="s">
         <v>28</v>
       </c>
       <c r="Q95" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="R95" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="S95" t="s">
         <v>159</v>
@@ -6586,37 +6595,37 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E96" t="s">
         <v>23</v>
       </c>
       <c r="F96" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H96" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I96" t="s">
         <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K96" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L96" t="s">
         <v>47</v>
@@ -6625,101 +6634,101 @@
         <v>48</v>
       </c>
       <c r="N96" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
       <c r="O96" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
       </c>
       <c r="Q96" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="R96" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="S96" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B97" t="s">
         <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E97" t="s">
         <v>23</v>
       </c>
       <c r="F97" t="s">
+        <v>141</v>
+      </c>
+      <c r="G97" t="s">
+        <v>25</v>
+      </c>
+      <c r="H97" t="s">
+        <v>26</v>
+      </c>
+      <c r="I97" t="s">
+        <v>36</v>
+      </c>
+      <c r="J97" t="s">
+        <v>45</v>
+      </c>
+      <c r="K97" t="s">
+        <v>52</v>
+      </c>
+      <c r="L97" t="s">
+        <v>53</v>
+      </c>
+      <c r="M97" t="s">
+        <v>54</v>
+      </c>
+      <c r="N97" t="s">
+        <v>27</v>
+      </c>
+      <c r="O97" t="s">
+        <v>37</v>
+      </c>
+      <c r="P97" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>142</v>
+      </c>
+      <c r="R97" t="s">
+        <v>27</v>
+      </c>
+      <c r="S97" t="s">
         <v>161</v>
-      </c>
-      <c r="G97" t="s">
-        <v>35</v>
-      </c>
-      <c r="H97" t="s">
-        <v>27</v>
-      </c>
-      <c r="I97" t="s">
-        <v>36</v>
-      </c>
-      <c r="J97" t="s">
-        <v>50</v>
-      </c>
-      <c r="K97" t="s">
-        <v>51</v>
-      </c>
-      <c r="L97" t="s">
-        <v>52</v>
-      </c>
-      <c r="M97" t="s">
-        <v>53</v>
-      </c>
-      <c r="N97" t="s">
-        <v>162</v>
-      </c>
-      <c r="O97" t="s">
-        <v>27</v>
-      </c>
-      <c r="P97" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>27</v>
-      </c>
-      <c r="R97" t="s">
-        <v>80</v>
-      </c>
-      <c r="S97" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
         <v>69</v>
       </c>
       <c r="D98" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E98" t="s">
         <v>23</v>
       </c>
       <c r="F98" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G98" t="s">
         <v>35</v>
@@ -6731,19 +6740,19 @@
         <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K98" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L98" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M98" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N98" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O98" t="s">
         <v>27</v>
@@ -6758,7 +6767,7 @@
         <v>80</v>
       </c>
       <c r="S98" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="99">
@@ -6766,19 +6775,19 @@
         <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C99" t="s">
         <v>69</v>
       </c>
       <c r="D99" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E99" t="s">
         <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G99" t="s">
         <v>35</v>
@@ -6790,19 +6799,19 @@
         <v>36</v>
       </c>
       <c r="J99" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K99" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L99" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M99" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="N99" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O99" t="s">
         <v>27</v>
@@ -6825,19 +6834,19 @@
         <v>167</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E100" t="s">
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G100" t="s">
         <v>35</v>
@@ -6849,19 +6858,19 @@
         <v>36</v>
       </c>
       <c r="J100" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K100" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L100" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M100" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N100" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O100" t="s">
         <v>27</v>
@@ -6890,13 +6899,13 @@
         <v>69</v>
       </c>
       <c r="D101" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E101" t="s">
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G101" t="s">
         <v>35</v>
@@ -6908,19 +6917,19 @@
         <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K101" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L101" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M101" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N101" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O101" t="s">
         <v>27</v>
@@ -6946,52 +6955,52 @@
         <v>21</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D102" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E102" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G102" t="s">
         <v>35</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I102" t="s">
         <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K102" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L102" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M102" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N102" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="O102" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
       </c>
       <c r="Q102" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="R102" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="S102" t="s">
         <v>169</v>
@@ -6999,66 +7008,66 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D103" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E103" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F103" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G103" t="s">
         <v>35</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I103" t="s">
         <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K103" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L103" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M103" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N103" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="O103" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
       </c>
       <c r="Q103" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="R103" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="S103" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B104" t="s">
         <v>21</v>
@@ -7067,13 +7076,13 @@
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E104" t="s">
         <v>69</v>
       </c>
       <c r="F104" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G104" t="s">
         <v>35</v>
@@ -7085,34 +7094,34 @@
         <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K104" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L104" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M104" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="N104" t="s">
         <v>27</v>
       </c>
       <c r="O104" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
       </c>
       <c r="Q104" t="s">
+        <v>173</v>
+      </c>
+      <c r="R104" t="s">
+        <v>27</v>
+      </c>
+      <c r="S104" t="s">
         <v>171</v>
-      </c>
-      <c r="R104" t="s">
-        <v>27</v>
-      </c>
-      <c r="S104" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="105">
@@ -7126,13 +7135,13 @@
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F105" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G105" t="s">
         <v>35</v>
@@ -7144,16 +7153,16 @@
         <v>36</v>
       </c>
       <c r="J105" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K105" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L105" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M105" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N105" t="s">
         <v>27</v>
@@ -7165,7 +7174,7 @@
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R105" t="s">
         <v>27</v>
@@ -7185,13 +7194,13 @@
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E106" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F106" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G106" t="s">
         <v>35</v>
@@ -7203,28 +7212,28 @@
         <v>36</v>
       </c>
       <c r="J106" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K106" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L106" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M106" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N106" t="s">
         <v>27</v>
       </c>
       <c r="O106" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
       </c>
       <c r="Q106" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R106" t="s">
         <v>27</v>
@@ -7244,13 +7253,13 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E107" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F107" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G107" t="s">
         <v>35</v>
@@ -7262,28 +7271,28 @@
         <v>36</v>
       </c>
       <c r="J107" t="s">
+        <v>37</v>
+      </c>
+      <c r="K107" t="s">
+        <v>38</v>
+      </c>
+      <c r="L107" t="s">
         <v>42</v>
       </c>
-      <c r="K107" t="s">
+      <c r="M107" t="s">
         <v>43</v>
       </c>
-      <c r="L107" t="s">
-        <v>47</v>
-      </c>
-      <c r="M107" t="s">
-        <v>48</v>
-      </c>
       <c r="N107" t="s">
         <v>27</v>
       </c>
       <c r="O107" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P107" t="s">
         <v>28</v>
       </c>
       <c r="Q107" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R107" t="s">
         <v>27</v>
@@ -7303,13 +7312,13 @@
         <v>20</v>
       </c>
       <c r="D108" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E108" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F108" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G108" t="s">
         <v>35</v>
@@ -7321,16 +7330,16 @@
         <v>36</v>
       </c>
       <c r="J108" t="s">
+        <v>37</v>
+      </c>
+      <c r="K108" t="s">
+        <v>38</v>
+      </c>
+      <c r="L108" t="s">
         <v>42</v>
       </c>
-      <c r="K108" t="s">
+      <c r="M108" t="s">
         <v>43</v>
-      </c>
-      <c r="L108" t="s">
-        <v>44</v>
-      </c>
-      <c r="M108" t="s">
-        <v>45</v>
       </c>
       <c r="N108" t="s">
         <v>27</v>
@@ -7342,7 +7351,7 @@
         <v>28</v>
       </c>
       <c r="Q108" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R108" t="s">
         <v>27</v>
@@ -7362,13 +7371,13 @@
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E109" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F109" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G109" t="s">
         <v>35</v>
@@ -7380,28 +7389,28 @@
         <v>36</v>
       </c>
       <c r="J109" t="s">
+        <v>37</v>
+      </c>
+      <c r="K109" t="s">
+        <v>38</v>
+      </c>
+      <c r="L109" t="s">
         <v>42</v>
       </c>
-      <c r="K109" t="s">
+      <c r="M109" t="s">
         <v>43</v>
       </c>
-      <c r="L109" t="s">
-        <v>44</v>
-      </c>
-      <c r="M109" t="s">
+      <c r="N109" t="s">
+        <v>27</v>
+      </c>
+      <c r="O109" t="s">
         <v>45</v>
       </c>
-      <c r="N109" t="s">
-        <v>27</v>
-      </c>
-      <c r="O109" t="s">
-        <v>42</v>
-      </c>
       <c r="P109" t="s">
         <v>28</v>
       </c>
       <c r="Q109" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R109" t="s">
         <v>27</v>
@@ -7421,13 +7430,13 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E110" t="s">
         <v>20</v>
       </c>
       <c r="F110" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G110" t="s">
         <v>35</v>
@@ -7439,28 +7448,28 @@
         <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L110" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M110" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N110" t="s">
         <v>27</v>
       </c>
       <c r="O110" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
       </c>
       <c r="Q110" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R110" t="s">
         <v>27</v>
@@ -7480,13 +7489,13 @@
         <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E111" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F111" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G111" t="s">
         <v>35</v>
@@ -7498,16 +7507,16 @@
         <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K111" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L111" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M111" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N111" t="s">
         <v>27</v>
@@ -7519,7 +7528,7 @@
         <v>28</v>
       </c>
       <c r="Q111" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R111" t="s">
         <v>27</v>
@@ -7539,13 +7548,13 @@
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E112" t="s">
         <v>20</v>
       </c>
       <c r="F112" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G112" t="s">
         <v>35</v>
@@ -7557,28 +7566,28 @@
         <v>36</v>
       </c>
       <c r="J112" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K112" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L112" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M112" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N112" t="s">
         <v>27</v>
       </c>
       <c r="O112" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
       </c>
       <c r="Q112" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R112" t="s">
         <v>27</v>
@@ -7598,13 +7607,13 @@
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E113" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="F113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G113" t="s">
         <v>35</v>
@@ -7616,28 +7625,28 @@
         <v>36</v>
       </c>
       <c r="J113" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K113" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L113" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M113" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N113" t="s">
         <v>27</v>
       </c>
       <c r="O113" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
       </c>
       <c r="Q113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R113" t="s">
         <v>27</v>
@@ -7657,13 +7666,13 @@
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E114" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F114" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G114" t="s">
         <v>35</v>
@@ -7675,16 +7684,16 @@
         <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K114" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L114" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M114" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N114" t="s">
         <v>27</v>
@@ -7696,7 +7705,7 @@
         <v>28</v>
       </c>
       <c r="Q114" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R114" t="s">
         <v>27</v>
@@ -7716,13 +7725,13 @@
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E115" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G115" t="s">
         <v>35</v>
@@ -7734,28 +7743,28 @@
         <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K115" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L115" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M115" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N115" t="s">
         <v>27</v>
       </c>
       <c r="O115" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
       </c>
       <c r="Q115" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R115" t="s">
         <v>27</v>
@@ -7775,13 +7784,13 @@
         <v>20</v>
       </c>
       <c r="D116" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E116" t="s">
         <v>23</v>
       </c>
       <c r="F116" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G116" t="s">
         <v>35</v>
@@ -7793,28 +7802,28 @@
         <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K116" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L116" t="s">
+        <v>53</v>
+      </c>
+      <c r="M116" t="s">
+        <v>54</v>
+      </c>
+      <c r="N116" t="s">
+        <v>27</v>
+      </c>
+      <c r="O116" t="s">
         <v>58</v>
       </c>
-      <c r="M116" t="s">
-        <v>59</v>
-      </c>
-      <c r="N116" t="s">
-        <v>27</v>
-      </c>
-      <c r="O116" t="s">
-        <v>50</v>
-      </c>
       <c r="P116" t="s">
         <v>28</v>
       </c>
       <c r="Q116" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R116" t="s">
         <v>27</v>
@@ -7834,34 +7843,34 @@
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E117" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F117" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G117" t="s">
         <v>35</v>
       </c>
       <c r="H117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I117" t="s">
         <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K117" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L117" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M117" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N117" t="s">
         <v>27</v>
@@ -7873,7 +7882,7 @@
         <v>28</v>
       </c>
       <c r="Q117" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R117" t="s">
         <v>27</v>
@@ -7893,46 +7902,46 @@
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E118" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F118" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G118" t="s">
         <v>35</v>
       </c>
       <c r="H118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I118" t="s">
         <v>36</v>
       </c>
       <c r="J118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K118" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L118" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M118" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N118" t="s">
         <v>27</v>
       </c>
       <c r="O118" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P118" t="s">
         <v>28</v>
       </c>
       <c r="Q118" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R118" t="s">
         <v>27</v>
@@ -7952,13 +7961,13 @@
         <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G119" t="s">
         <v>35</v>
@@ -7970,28 +7979,28 @@
         <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K119" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="L119" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M119" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="N119" t="s">
         <v>27</v>
       </c>
       <c r="O119" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P119" t="s">
         <v>28</v>
       </c>
       <c r="Q119" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R119" t="s">
         <v>27</v>
@@ -8011,13 +8020,13 @@
         <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E120" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G120" t="s">
         <v>35</v>
@@ -8029,16 +8038,16 @@
         <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K120" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L120" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M120" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N120" t="s">
         <v>27</v>
@@ -8050,7 +8059,7 @@
         <v>28</v>
       </c>
       <c r="Q120" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R120" t="s">
         <v>27</v>
@@ -8070,13 +8079,13 @@
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E121" t="s">
         <v>23</v>
       </c>
       <c r="F121" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G121" t="s">
         <v>35</v>
@@ -8088,28 +8097,28 @@
         <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K121" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L121" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M121" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N121" t="s">
         <v>27</v>
       </c>
       <c r="O121" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P121" t="s">
         <v>28</v>
       </c>
       <c r="Q121" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R121" t="s">
         <v>27</v>
@@ -8129,13 +8138,13 @@
         <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E122" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G122" t="s">
         <v>35</v>
@@ -8147,28 +8156,28 @@
         <v>36</v>
       </c>
       <c r="J122" t="s">
+        <v>37</v>
+      </c>
+      <c r="K122" t="s">
+        <v>38</v>
+      </c>
+      <c r="L122" t="s">
         <v>42</v>
       </c>
-      <c r="K122" t="s">
+      <c r="M122" t="s">
         <v>43</v>
       </c>
-      <c r="L122" t="s">
-        <v>47</v>
-      </c>
-      <c r="M122" t="s">
-        <v>48</v>
-      </c>
       <c r="N122" t="s">
         <v>27</v>
       </c>
       <c r="O122" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P122" t="s">
         <v>28</v>
       </c>
       <c r="Q122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R122" t="s">
         <v>27</v>
@@ -8188,13 +8197,13 @@
         <v>20</v>
       </c>
       <c r="D123" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E123" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F123" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G123" t="s">
         <v>35</v>
@@ -8206,16 +8215,16 @@
         <v>36</v>
       </c>
       <c r="J123" t="s">
+        <v>37</v>
+      </c>
+      <c r="K123" t="s">
+        <v>38</v>
+      </c>
+      <c r="L123" t="s">
         <v>42</v>
       </c>
-      <c r="K123" t="s">
+      <c r="M123" t="s">
         <v>43</v>
-      </c>
-      <c r="L123" t="s">
-        <v>44</v>
-      </c>
-      <c r="M123" t="s">
-        <v>45</v>
       </c>
       <c r="N123" t="s">
         <v>27</v>
@@ -8227,7 +8236,7 @@
         <v>28</v>
       </c>
       <c r="Q123" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R123" t="s">
         <v>27</v>
@@ -8247,13 +8256,13 @@
         <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E124" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F124" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G124" t="s">
         <v>35</v>
@@ -8265,28 +8274,28 @@
         <v>36</v>
       </c>
       <c r="J124" t="s">
+        <v>37</v>
+      </c>
+      <c r="K124" t="s">
+        <v>38</v>
+      </c>
+      <c r="L124" t="s">
         <v>42</v>
       </c>
-      <c r="K124" t="s">
+      <c r="M124" t="s">
         <v>43</v>
       </c>
-      <c r="L124" t="s">
-        <v>44</v>
-      </c>
-      <c r="M124" t="s">
+      <c r="N124" t="s">
+        <v>27</v>
+      </c>
+      <c r="O124" t="s">
         <v>45</v>
       </c>
-      <c r="N124" t="s">
-        <v>27</v>
-      </c>
-      <c r="O124" t="s">
-        <v>42</v>
-      </c>
       <c r="P124" t="s">
         <v>28</v>
       </c>
       <c r="Q124" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R124" t="s">
         <v>27</v>
@@ -8306,13 +8315,13 @@
         <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E125" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F125" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G125" t="s">
         <v>35</v>
@@ -8324,28 +8333,28 @@
         <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K125" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L125" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M125" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N125" t="s">
         <v>27</v>
       </c>
       <c r="O125" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P125" t="s">
         <v>28</v>
       </c>
       <c r="Q125" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R125" t="s">
         <v>27</v>
@@ -8365,13 +8374,13 @@
         <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E126" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G126" t="s">
         <v>35</v>
@@ -8383,28 +8392,28 @@
         <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K126" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L126" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M126" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N126" t="s">
         <v>27</v>
       </c>
       <c r="O126" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P126" t="s">
         <v>28</v>
       </c>
       <c r="Q126" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R126" t="s">
         <v>27</v>
@@ -8424,13 +8433,13 @@
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E127" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F127" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G127" t="s">
         <v>35</v>
@@ -8442,28 +8451,28 @@
         <v>36</v>
       </c>
       <c r="J127" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K127" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L127" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M127" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N127" t="s">
         <v>27</v>
       </c>
       <c r="O127" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P127" t="s">
         <v>28</v>
       </c>
       <c r="Q127" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R127" t="s">
         <v>27</v>
@@ -8483,13 +8492,13 @@
         <v>20</v>
       </c>
       <c r="D128" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E128" t="s">
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G128" t="s">
         <v>35</v>
@@ -8501,16 +8510,16 @@
         <v>36</v>
       </c>
       <c r="J128" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K128" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L128" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M128" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N128" t="s">
         <v>27</v>
@@ -8522,7 +8531,7 @@
         <v>28</v>
       </c>
       <c r="Q128" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R128" t="s">
         <v>27</v>
@@ -8542,13 +8551,13 @@
         <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E129" t="s">
         <v>23</v>
       </c>
       <c r="F129" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G129" t="s">
         <v>35</v>
@@ -8560,28 +8569,28 @@
         <v>36</v>
       </c>
       <c r="J129" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K129" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L129" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M129" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N129" t="s">
         <v>27</v>
       </c>
       <c r="O129" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P129" t="s">
         <v>28</v>
       </c>
       <c r="Q129" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R129" t="s">
         <v>27</v>
@@ -8601,13 +8610,13 @@
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E130" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G130" t="s">
         <v>35</v>
@@ -8619,28 +8628,28 @@
         <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K130" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L130" t="s">
+        <v>53</v>
+      </c>
+      <c r="M130" t="s">
+        <v>54</v>
+      </c>
+      <c r="N130" t="s">
+        <v>27</v>
+      </c>
+      <c r="O130" t="s">
         <v>58</v>
       </c>
-      <c r="M130" t="s">
-        <v>59</v>
-      </c>
-      <c r="N130" t="s">
-        <v>27</v>
-      </c>
-      <c r="O130" t="s">
-        <v>50</v>
-      </c>
       <c r="P130" t="s">
         <v>28</v>
       </c>
       <c r="Q130" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R130" t="s">
         <v>27</v>
@@ -8657,52 +8666,52 @@
         <v>21</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="E131" t="s">
         <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="G131" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="H131" t="s">
         <v>26</v>
       </c>
       <c r="I131" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J131" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K131" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L131" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M131" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="N131" t="s">
         <v>27</v>
       </c>
       <c r="O131" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="P131" t="s">
         <v>28</v>
       </c>
       <c r="Q131" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="R131" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S131" t="s">
         <v>200</v>
@@ -8710,69 +8719,69 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="E132" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F132" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="G132" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="H132" t="s">
         <v>26</v>
       </c>
       <c r="I132" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K132" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L132" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M132" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="N132" t="s">
         <v>27</v>
       </c>
       <c r="O132" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="P132" t="s">
         <v>28</v>
       </c>
       <c r="Q132" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="R132" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S132" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C133" t="s">
         <v>21</v>
@@ -8784,13 +8793,13 @@
         <v>23</v>
       </c>
       <c r="F133" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G133" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H133" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I133" t="s">
         <v>27</v>
@@ -8823,7 +8832,7 @@
         <v>24</v>
       </c>
       <c r="S133" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="134">
@@ -8831,40 +8840,40 @@
         <v>205</v>
       </c>
       <c r="B134" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C134" t="s">
         <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="E134" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F134" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="H134" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I134" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J134" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K134" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L134" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="M134" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N134" t="s">
         <v>27</v>
@@ -8876,10 +8885,10 @@
         <v>28</v>
       </c>
       <c r="Q134" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="R134" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="S134" t="s">
         <v>205</v>
@@ -8890,40 +8899,40 @@
         <v>206</v>
       </c>
       <c r="B135" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C135" t="s">
         <v>21</v>
       </c>
       <c r="D135" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F135" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="H135" t="s">
         <v>30</v>
       </c>
       <c r="I135" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J135" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K135" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L135" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="M135" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="N135" t="s">
         <v>27</v>
@@ -8935,10 +8944,10 @@
         <v>28</v>
       </c>
       <c r="Q135" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="R135" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="S135" t="s">
         <v>206</v>
@@ -8955,13 +8964,13 @@
         <v>21</v>
       </c>
       <c r="D136" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E136" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F136" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G136" t="s">
         <v>25</v>
@@ -8973,16 +8982,16 @@
         <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="K136" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L136" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M136" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N136" t="s">
         <v>27</v>
@@ -8994,10 +9003,10 @@
         <v>28</v>
       </c>
       <c r="Q136" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R136" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S136" t="s">
         <v>207</v>
@@ -9014,13 +9023,13 @@
         <v>21</v>
       </c>
       <c r="D137" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E137" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F137" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G137" t="s">
         <v>25</v>
@@ -9032,16 +9041,16 @@
         <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K137" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="L137" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M137" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="N137" t="s">
         <v>27</v>
@@ -9053,10 +9062,10 @@
         <v>28</v>
       </c>
       <c r="Q137" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R137" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S137" t="s">
         <v>208</v>
@@ -9073,13 +9082,13 @@
         <v>21</v>
       </c>
       <c r="D138" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E138" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F138" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G138" t="s">
         <v>25</v>
@@ -9091,31 +9100,31 @@
         <v>36</v>
       </c>
       <c r="J138" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K138" t="s">
+        <v>38</v>
+      </c>
+      <c r="L138" t="s">
+        <v>39</v>
+      </c>
+      <c r="M138" t="s">
+        <v>40</v>
+      </c>
+      <c r="N138" t="s">
+        <v>27</v>
+      </c>
+      <c r="O138" t="s">
+        <v>27</v>
+      </c>
+      <c r="P138" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q138" t="s">
         <v>57</v>
       </c>
-      <c r="L138" t="s">
-        <v>58</v>
-      </c>
-      <c r="M138" t="s">
-        <v>59</v>
-      </c>
-      <c r="N138" t="s">
-        <v>27</v>
-      </c>
-      <c r="O138" t="s">
-        <v>27</v>
-      </c>
-      <c r="P138" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>62</v>
-      </c>
       <c r="R138" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S138" t="s">
         <v>209</v>
@@ -9132,34 +9141,34 @@
         <v>21</v>
       </c>
       <c r="D139" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E139" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F139" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G139" t="s">
         <v>25</v>
       </c>
       <c r="H139" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I139" t="s">
         <v>36</v>
       </c>
       <c r="J139" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K139" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L139" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M139" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N139" t="s">
         <v>27</v>
@@ -9171,10 +9180,10 @@
         <v>28</v>
       </c>
       <c r="Q139" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R139" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S139" t="s">
         <v>210</v>
@@ -9191,34 +9200,34 @@
         <v>21</v>
       </c>
       <c r="D140" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E140" t="s">
         <v>69</v>
       </c>
       <c r="F140" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G140" t="s">
         <v>25</v>
       </c>
       <c r="H140" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I140" t="s">
         <v>36</v>
       </c>
       <c r="J140" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K140" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="L140" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="M140" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N140" t="s">
         <v>27</v>
@@ -9230,10 +9239,10 @@
         <v>28</v>
       </c>
       <c r="Q140" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R140" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S140" t="s">
         <v>211</v>
@@ -9250,13 +9259,13 @@
         <v>21</v>
       </c>
       <c r="D141" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E141" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F141" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G141" t="s">
         <v>25</v>
@@ -9268,34 +9277,211 @@
         <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K141" t="s">
+        <v>59</v>
+      </c>
+      <c r="L141" t="s">
+        <v>60</v>
+      </c>
+      <c r="M141" t="s">
+        <v>61</v>
+      </c>
+      <c r="N141" t="s">
+        <v>27</v>
+      </c>
+      <c r="O141" t="s">
+        <v>27</v>
+      </c>
+      <c r="P141" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q141" t="s">
         <v>57</v>
       </c>
-      <c r="L141" t="s">
-        <v>58</v>
-      </c>
-      <c r="M141" t="s">
-        <v>59</v>
-      </c>
-      <c r="N141" t="s">
-        <v>27</v>
-      </c>
-      <c r="O141" t="s">
-        <v>27</v>
-      </c>
-      <c r="P141" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q141" t="s">
-        <v>62</v>
-      </c>
       <c r="R141" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="S141" t="s">
         <v>212</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>213</v>
+      </c>
+      <c r="B142" t="s">
+        <v>21</v>
+      </c>
+      <c r="C142" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" t="s">
+        <v>56</v>
+      </c>
+      <c r="E142" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142" t="s">
+        <v>57</v>
+      </c>
+      <c r="G142" t="s">
+        <v>25</v>
+      </c>
+      <c r="H142" t="s">
+        <v>26</v>
+      </c>
+      <c r="I142" t="s">
+        <v>36</v>
+      </c>
+      <c r="J142" t="s">
+        <v>45</v>
+      </c>
+      <c r="K142" t="s">
+        <v>46</v>
+      </c>
+      <c r="L142" t="s">
+        <v>47</v>
+      </c>
+      <c r="M142" t="s">
+        <v>48</v>
+      </c>
+      <c r="N142" t="s">
+        <v>27</v>
+      </c>
+      <c r="O142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P142" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>57</v>
+      </c>
+      <c r="R142" t="s">
+        <v>57</v>
+      </c>
+      <c r="S142" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>214</v>
+      </c>
+      <c r="B143" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" t="s">
+        <v>56</v>
+      </c>
+      <c r="E143" t="s">
+        <v>69</v>
+      </c>
+      <c r="F143" t="s">
+        <v>57</v>
+      </c>
+      <c r="G143" t="s">
+        <v>25</v>
+      </c>
+      <c r="H143" t="s">
+        <v>26</v>
+      </c>
+      <c r="I143" t="s">
+        <v>36</v>
+      </c>
+      <c r="J143" t="s">
+        <v>37</v>
+      </c>
+      <c r="K143" t="s">
+        <v>38</v>
+      </c>
+      <c r="L143" t="s">
+        <v>39</v>
+      </c>
+      <c r="M143" t="s">
+        <v>40</v>
+      </c>
+      <c r="N143" t="s">
+        <v>27</v>
+      </c>
+      <c r="O143" t="s">
+        <v>27</v>
+      </c>
+      <c r="P143" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>57</v>
+      </c>
+      <c r="R143" t="s">
+        <v>57</v>
+      </c>
+      <c r="S143" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>215</v>
+      </c>
+      <c r="B144" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" t="s">
+        <v>56</v>
+      </c>
+      <c r="E144" t="s">
+        <v>23</v>
+      </c>
+      <c r="F144" t="s">
+        <v>57</v>
+      </c>
+      <c r="G144" t="s">
+        <v>25</v>
+      </c>
+      <c r="H144" t="s">
+        <v>26</v>
+      </c>
+      <c r="I144" t="s">
+        <v>36</v>
+      </c>
+      <c r="J144" t="s">
+        <v>45</v>
+      </c>
+      <c r="K144" t="s">
+        <v>52</v>
+      </c>
+      <c r="L144" t="s">
+        <v>53</v>
+      </c>
+      <c r="M144" t="s">
+        <v>54</v>
+      </c>
+      <c r="N144" t="s">
+        <v>27</v>
+      </c>
+      <c r="O144" t="s">
+        <v>27</v>
+      </c>
+      <c r="P144" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>57</v>
+      </c>
+      <c r="R144" t="s">
+        <v>57</v>
+      </c>
+      <c r="S144" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
